--- a/output/stock_quant_scores/TSMC34.SA_balance_df.xlsx
+++ b/output/stock_quant_scores/TSMC34.SA_balance_df.xlsx
@@ -2006,28 +2006,38 @@
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr"/>
+      <c r="E6" t="n">
+        <v>753631900000</v>
+      </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr"/>
+      <c r="H6" t="n">
+        <v>848720100000</v>
+      </c>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
-      <c r="O6" t="inlineStr"/>
+      <c r="O6" t="n">
+        <v>2149259800000</v>
+      </c>
       <c r="P6" t="inlineStr"/>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr"/>
       <c r="S6" t="inlineStr"/>
       <c r="T6" t="inlineStr"/>
       <c r="U6" t="inlineStr"/>
-      <c r="V6" t="inlineStr"/>
+      <c r="V6" t="n">
+        <v>1887802900000</v>
+      </c>
       <c r="W6" t="inlineStr"/>
       <c r="X6" t="inlineStr"/>
       <c r="Y6" t="inlineStr"/>
-      <c r="Z6" t="inlineStr"/>
+      <c r="Z6" t="n">
+        <v>1573619700000</v>
+      </c>
       <c r="AA6" t="inlineStr"/>
       <c r="AB6" t="inlineStr"/>
       <c r="AC6" t="inlineStr"/>
@@ -2040,7 +2050,9 @@
       <c r="AH6" t="inlineStr"/>
       <c r="AI6" t="inlineStr"/>
       <c r="AJ6" t="inlineStr"/>
-      <c r="AK6" t="inlineStr"/>
+      <c r="AK6" t="n">
+        <v>758352800000</v>
+      </c>
       <c r="AL6" t="inlineStr"/>
       <c r="AM6" t="inlineStr"/>
       <c r="AN6" t="inlineStr"/>
@@ -2055,7 +2067,9 @@
       <c r="AW6" t="inlineStr"/>
       <c r="AX6" t="inlineStr"/>
       <c r="AY6" t="inlineStr"/>
-      <c r="AZ6" t="inlineStr"/>
+      <c r="AZ6" t="n">
+        <v>3725302200000</v>
+      </c>
       <c r="BA6" t="inlineStr"/>
       <c r="BB6" t="inlineStr"/>
       <c r="BC6" t="inlineStr"/>
@@ -2080,10 +2094,14 @@
       <c r="BV6" t="inlineStr"/>
       <c r="BW6" t="inlineStr"/>
       <c r="BX6" t="inlineStr"/>
-      <c r="BY6" t="inlineStr"/>
+      <c r="BY6" t="n">
+        <v>1607072900000</v>
+      </c>
       <c r="BZ6" t="inlineStr"/>
       <c r="CA6" t="inlineStr"/>
-      <c r="CB6" t="inlineStr"/>
+      <c r="CB6" t="n">
+        <v>193102300000</v>
+      </c>
       <c r="CC6" t="inlineStr"/>
       <c r="CD6" t="inlineStr"/>
       <c r="CE6" t="inlineStr"/>
@@ -2101,7 +2119,9 @@
       </c>
       <c r="CL6" t="inlineStr"/>
       <c r="CM6" t="inlineStr"/>
-      <c r="CN6" t="inlineStr"/>
+      <c r="CN6" t="n">
+        <v>1064990200000</v>
+      </c>
       <c r="CO6" t="inlineStr"/>
       <c r="CP6" t="inlineStr"/>
     </row>
